--- a/OMOP Analysis/Results/Output_yearly_costs_Raw-Unadjusted.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_costs_Raw-Unadjusted.xlsx
@@ -422,7 +422,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>597.42</v>
+        <v>560.91</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -431,28 +431,28 @@
         <v>8960.83</v>
       </c>
       <c r="E2">
-        <v>622.11</v>
+        <v>555.8099999999999</v>
       </c>
       <c r="F2">
-        <v>412.78</v>
+        <v>397.2</v>
       </c>
       <c r="G2">
         <v>168</v>
       </c>
       <c r="H2">
-        <v>798</v>
+        <v>756</v>
       </c>
       <c r="I2">
         <v>16978</v>
       </c>
       <c r="J2">
-        <v>4.77</v>
+        <v>4.27</v>
       </c>
       <c r="K2">
-        <v>588.0599999999999</v>
+        <v>552.55</v>
       </c>
       <c r="L2">
-        <v>606.78</v>
+        <v>569.27</v>
       </c>
     </row>
     <row r="3">
@@ -460,16 +460,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>323.45</v>
+        <v>304.38</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>8576.99</v>
+        <v>6332.79</v>
       </c>
       <c r="E3">
-        <v>529.65</v>
+        <v>481.23</v>
       </c>
       <c r="F3">
         <v>84</v>
@@ -478,19 +478,19 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>462</v>
+        <v>458.39</v>
       </c>
       <c r="I3">
         <v>16978</v>
       </c>
       <c r="J3">
-        <v>4.06</v>
+        <v>3.69</v>
       </c>
       <c r="K3">
-        <v>315.48</v>
+        <v>297.14</v>
       </c>
       <c r="L3">
-        <v>331.42</v>
+        <v>311.62</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +570,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>572.89</v>
+        <v>537.88</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -579,28 +579,28 @@
         <v>8960.83</v>
       </c>
       <c r="E2">
-        <v>620.63</v>
+        <v>555.54</v>
       </c>
       <c r="F2">
         <v>378</v>
       </c>
       <c r="G2">
-        <v>157.72</v>
+        <v>152.75</v>
       </c>
       <c r="H2">
-        <v>775.2</v>
+        <v>734.35</v>
       </c>
       <c r="I2">
         <v>17705</v>
       </c>
       <c r="J2">
-        <v>4.66</v>
+        <v>4.18</v>
       </c>
       <c r="K2">
-        <v>563.74</v>
+        <v>529.6900000000001</v>
       </c>
       <c r="L2">
-        <v>582.03</v>
+        <v>546.0599999999999</v>
       </c>
     </row>
     <row r="3">
@@ -608,16 +608,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>310.17</v>
+        <v>291.88</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>8576.99</v>
+        <v>6332.79</v>
       </c>
       <c r="E3">
-        <v>522.61</v>
+        <v>475.1</v>
       </c>
       <c r="F3">
         <v>42</v>
@@ -626,19 +626,19 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>443.96</v>
+        <v>427.38</v>
       </c>
       <c r="I3">
         <v>17705</v>
       </c>
       <c r="J3">
-        <v>3.93</v>
+        <v>3.57</v>
       </c>
       <c r="K3">
-        <v>302.47</v>
+        <v>284.88</v>
       </c>
       <c r="L3">
-        <v>317.87</v>
+        <v>298.88</v>
       </c>
     </row>
   </sheetData>
